--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_08/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_08/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>63.15</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>19.81</v>
+        <v>18.68</v>
       </c>
       <c r="E2" t="n">
-        <v>31.38</v>
+        <v>28.7</v>
       </c>
       <c r="F2" t="n">
-        <v>40.21</v>
+        <v>43.05</v>
       </c>
       <c r="G2" t="n">
-        <v>44.5</v>
+        <v>48.22</v>
       </c>
       <c r="H2" t="n">
-        <v>58.69</v>
+        <v>59.78</v>
       </c>
       <c r="I2" t="n">
-        <v>80.05</v>
+        <v>79.93000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>59.79</v>
+        <v>56.94</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89</v>
+        <v>40.19</v>
       </c>
       <c r="D3" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="E3" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="F3" t="n">
-        <v>40.48</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>45.93</v>
+        <v>40.01</v>
       </c>
       <c r="H3" t="n">
-        <v>45.96</v>
+        <v>40.01</v>
       </c>
       <c r="I3" t="n">
-        <v>46.12</v>
+        <v>40.06</v>
       </c>
       <c r="J3" t="n">
-        <v>46.87</v>
+        <v>45.7</v>
       </c>
       <c r="K3" t="n">
-        <v>6.38</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="E4" t="n">
-        <v>16.3</v>
+        <v>15.79</v>
       </c>
       <c r="F4" t="n">
-        <v>6.29</v>
+        <v>6.86</v>
       </c>
       <c r="G4" t="n">
-        <v>7.73</v>
+        <v>7.93</v>
       </c>
       <c r="H4" t="n">
-        <v>8.1</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>10.24</v>
+        <v>9.93</v>
       </c>
       <c r="J4" t="n">
-        <v>11.41</v>
+        <v>11.72</v>
       </c>
       <c r="K4" t="n">
-        <v>5.12</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>105.61</v>
+        <v>91.78</v>
       </c>
       <c r="D5" t="n">
-        <v>10.9</v>
+        <v>28.23</v>
       </c>
       <c r="E5" t="n">
-        <v>10.32</v>
+        <v>30.75</v>
       </c>
       <c r="F5" t="n">
-        <v>83.83</v>
+        <v>59.02</v>
       </c>
       <c r="G5" t="n">
-        <v>95.98</v>
+        <v>75.64</v>
       </c>
       <c r="H5" t="n">
-        <v>107.04</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>110.93</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>137.61</v>
+        <v>174.7</v>
       </c>
       <c r="K5" t="n">
-        <v>53.78</v>
+        <v>115.68</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="F6" t="n">
         <v>4.03</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E6" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.95</v>
-      </c>
       <c r="G6" t="n">
-        <v>3.81</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.02</v>
+        <v>4.44</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.65</v>
       </c>
       <c r="J6" t="n">
-        <v>4.84</v>
+        <v>4.96</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9</v>
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
